--- a/data/trans_dic/IP25-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que ven la televisión todos o casi todos los días</t>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -537,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -575,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -631,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -663,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>86,1%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -716,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,15; 92,25</t>
+          <t>81,59; 92,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,24; 93,8</t>
+          <t>83,31; 93,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,33; 90,77</t>
+          <t>78,74; 91,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>78,96; 90,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,32; 90,23</t>
+          <t>84,25; 94,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,43; 94,15</t>
+          <t>80,0; 91,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,09; 91,32</t>
+          <t>82,18; 89,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>85,37; 92,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,21; 89,81</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>85,2; 92,82</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81,4; 89,84</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,58</t>
+          <t>81,58; 89,94</t>
         </is>
       </c>
     </row>
@@ -803,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>90,34%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -856,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,98; 93,09</t>
+          <t>81,87; 93,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,83; 93,8</t>
+          <t>83,82; 93,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,75; 93,25</t>
+          <t>83,91; 93,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>75,49; 88,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,09; 88,86</t>
+          <t>83,45; 93,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,55; 94,22</t>
+          <t>86,62; 94,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,34; 94,91</t>
+          <t>80,38; 89,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>85,54; 92,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,99; 89,61</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>85,56; 92,81</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>87,04; 93,11</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,7</t>
+          <t>86,83; 93,18</t>
         </is>
       </c>
     </row>
@@ -943,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>90,42%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>91,01%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -996,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,21; 95,08</t>
+          <t>82,71; 94,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,05; 94,63</t>
+          <t>84,32; 94,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,74; 96,33</t>
+          <t>85,31; 96,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>86,26; 95,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,27; 95,3</t>
+          <t>83,22; 94,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,19; 94,75</t>
+          <t>83,64; 94,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,67; 94,78</t>
+          <t>86,84; 94,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>86,37; 93,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,82; 93,99</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>86,39; 93,71</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>86,66; 94,27</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,2</t>
+          <t>86,54; 94,24</t>
         </is>
       </c>
     </row>
@@ -1083,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>91,66%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,69; 94,0</t>
+          <t>87,64; 94,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,29; 90,26</t>
+          <t>82,16; 90,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,23; 93,47</t>
+          <t>87,2; 93,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>84,23; 91,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,82; 91,06</t>
+          <t>89,48; 95,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,45; 95,56</t>
+          <t>89,36; 95,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,15; 95,2</t>
+          <t>87,03; 91,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>87,5; 92,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,02; 92,11</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>87,37; 92,07</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>89,38; 93,78</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,34</t>
+          <t>89,19; 93,69</t>
         </is>
       </c>
     </row>
@@ -1223,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>89,3%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>90,82%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,43; 96,45</t>
+          <t>88,38; 96,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,49; 92,23</t>
+          <t>83,62; 92,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,98; 94,63</t>
+          <t>86,91; 94,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>82,23; 91,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,94; 92,16</t>
+          <t>85,35; 94,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,77; 93,99</t>
+          <t>85,82; 94,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,7; 94,18</t>
+          <t>86,44; 92,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>86,1; 92,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,23; 92,82</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>85,64; 92,01</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>87,59; 93,32</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,51</t>
+          <t>87,52; 93,43</t>
         </is>
       </c>
     </row>
@@ -1363,47 +1190,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>89,94%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>92,56%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,57; 96,23</t>
+          <t>85,51; 96,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,2; 95,03</t>
+          <t>82,43; 95,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82,11; 94,27</t>
+          <t>81,72; 93,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>84,33; 95,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,86; 95,3</t>
+          <t>83,23; 94,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,27; 94,46</t>
+          <t>89,59; 99,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,8; 98,91</t>
+          <t>86,37; 94,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>84,96; 93,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86,56; 94,77</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>84,99; 93,66</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>88,1; 95,76</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,01</t>
+          <t>88,6; 95,62</t>
         </is>
       </c>
     </row>
@@ -1503,47 +1300,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>90,56%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,62; 92,32</t>
+          <t>88,53; 92,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,46; 90,42</t>
+          <t>86,51; 90,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,0; 91,75</t>
+          <t>87,85; 91,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>85,59; 89,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,52; 89,57</t>
+          <t>89,11; 92,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,09; 92,71</t>
+          <t>89,46; 92,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,27; 92,77</t>
+          <t>87,55; 90,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>88,38; 91,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,51; 90,32</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>88,39; 91,1</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>89,19; 91,75</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,1</t>
+          <t>89,27; 91,75</t>
         </is>
       </c>
     </row>
@@ -1624,18 +1391,1297 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>90485</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80289</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70978</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83040</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80133</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86493</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>173525</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>160424</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>157470</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>84542; 95540</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74922; 84514</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65421; 76104</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77024; 87973</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>74998; 84093</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>79837; 91306</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>165309; 180192</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>152773; 166153</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>149200; 164483</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>77447</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>83334</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>94372</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70879</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86904</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>102976</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>148326</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>170239</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>197348</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>71548; 81367</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>78178; 87212</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>88700; 98999</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>64903; 76190</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>80763; 90950</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>97658; 107077</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>139341; 154701</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>162559; 176260</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>189690; 203550</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>60034</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78040</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57022</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>90904</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77846</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67900</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>150938</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>155886</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>124922</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>55150; 63238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>72645; 81487</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52757; 59537</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>85681; 95209</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>71770; 81586</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>63090; 71573</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>144161; 156206</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>148910; 161530</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>118789; 129365</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>182742</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>178955</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202594</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>178337</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>210963</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>195605</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>361078</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>389918</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>398199</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>175930; 188829</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169342; 185836</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>194967; 208244</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170209; 185398</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>203223; 216575</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>188421; 200705</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>350571; 370262</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>379092; 399347</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>387463; 407026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>97014</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>130826</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124292</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>111290</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>126914</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>129347</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>208305</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>257740</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>253639</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>92026; 100360</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123944; 136557</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>118369; 128628</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>104668; 116851</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>119838; 132202</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>122802; 134653</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>200024; 214666</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>248504; 265855</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>244414; 260929</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>68921</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48589</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>54332</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66491</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>64988</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>134434</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>115080</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>119320</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>64018; 72016</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>44438; 51376</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49922; 57391</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>61048; 68912</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>61620; 69935</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>60766; 67163</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>127184; 139653</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>108701; 119884</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>114211; 123272</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1793</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>576643</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>600034</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>603589</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>599964</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>649253</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>647307</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1176607</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1249287</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1250897</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>564286; 587975</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>586162; 612749</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>589905; 613995</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>585939; 613042</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>635912; 661865</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>634913; 659523</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1157407; 1193433</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1229543; 1267704</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1232980; 1267254</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP25-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,59; 92,2</t>
+          <t>80,85; 92,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,31; 93,97</t>
+          <t>83,36; 93,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,74; 91,59</t>
+          <t>78,21; 91,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,96; 90,19</t>
+          <t>78,85; 90,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,25; 94,47</t>
+          <t>83,72; 94,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,0; 91,49</t>
+          <t>79,6; 91,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,18; 89,57</t>
+          <t>82,01; 89,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,37; 92,85</t>
+          <t>85,54; 93,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,58; 89,94</t>
+          <t>81,4; 89,82</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,87; 93,11</t>
+          <t>83,09; 93,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,82; 93,51</t>
+          <t>83,32; 93,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,91; 93,65</t>
+          <t>83,36; 93,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,49; 88,62</t>
+          <t>75,0; 87,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,45; 93,98</t>
+          <t>84,0; 94,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,62; 94,97</t>
+          <t>86,08; 95,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,38; 89,24</t>
+          <t>80,96; 89,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,54; 92,75</t>
+          <t>85,45; 92,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,83; 93,18</t>
+          <t>86,63; 93,05</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,71; 94,84</t>
+          <t>83,09; 95,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,32; 94,58</t>
+          <t>84,38; 95,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,31; 96,28</t>
+          <t>85,49; 96,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,26; 95,85</t>
+          <t>86,09; 95,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,22; 94,6</t>
+          <t>83,08; 94,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,64; 94,89</t>
+          <t>82,82; 94,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,84; 94,09</t>
+          <t>86,46; 93,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,37; 93,69</t>
+          <t>85,98; 93,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,54; 94,24</t>
+          <t>86,24; 94,24</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,64; 94,07</t>
+          <t>86,95; 93,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,16; 90,16</t>
+          <t>82,3; 90,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,2; 93,14</t>
+          <t>87,4; 93,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,23; 91,75</t>
+          <t>84,69; 91,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,48; 95,36</t>
+          <t>89,68; 95,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,36; 95,19</t>
+          <t>89,24; 95,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,03; 91,92</t>
+          <t>87,15; 92,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,5; 92,18</t>
+          <t>87,49; 92,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,19; 93,69</t>
+          <t>89,35; 93,56</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,38; 96,39</t>
+          <t>88,92; 96,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,62; 92,13</t>
+          <t>83,09; 91,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,91; 94,45</t>
+          <t>87,27; 94,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,23; 91,8</t>
+          <t>81,91; 91,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,35; 94,15</t>
+          <t>84,69; 93,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,82; 94,11</t>
+          <t>85,11; 93,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,44; 92,76</t>
+          <t>86,47; 92,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>86,1; 92,11</t>
+          <t>86,03; 92,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,52; 93,43</t>
+          <t>87,53; 93,16</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,51; 96,19</t>
+          <t>86,11; 95,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,43; 95,3</t>
+          <t>82,61; 95,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,72; 93,95</t>
+          <t>81,81; 94,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,33; 95,19</t>
+          <t>84,07; 95,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,23; 94,46</t>
+          <t>82,66; 94,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89,59; 99,02</t>
+          <t>89,84; 98,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,37; 94,83</t>
+          <t>86,76; 94,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,96; 93,7</t>
+          <t>84,86; 93,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,6; 95,62</t>
+          <t>88,17; 95,84</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,53; 92,24</t>
+          <t>88,47; 92,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,51; 90,43</t>
+          <t>86,38; 90,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,85; 91,44</t>
+          <t>87,78; 91,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85,59; 89,55</t>
+          <t>85,37; 89,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,11; 92,75</t>
+          <t>89,12; 92,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,46; 92,92</t>
+          <t>89,06; 92,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,55; 90,27</t>
+          <t>87,6; 90,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,38; 91,12</t>
+          <t>88,41; 91,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,27; 91,75</t>
+          <t>89,31; 91,82</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84542; 95540</t>
+          <t>83774; 95375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74922; 84514</t>
+          <t>74965; 84531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65421; 76104</t>
+          <t>64987; 75828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77024; 87973</t>
+          <t>76910; 88132</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74998; 84093</t>
+          <t>74525; 84071</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79837; 91306</t>
+          <t>79442; 91039</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>165309; 180192</t>
+          <t>164967; 180960</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>152773; 166153</t>
+          <t>153070; 166574</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149200; 164483</t>
+          <t>148877; 164277</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71548; 81367</t>
+          <t>72609; 81549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78178; 87212</t>
+          <t>77707; 87475</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88700; 98999</t>
+          <t>88126; 98597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64903; 76190</t>
+          <t>64479; 75555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80763; 90950</t>
+          <t>81289; 91268</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>97658; 107077</t>
+          <t>97057; 107126</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>139341; 154701</t>
+          <t>140349; 155315</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>162559; 176260</t>
+          <t>162401; 176315</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>189690; 203550</t>
+          <t>189262; 203285</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55150; 63238</t>
+          <t>55408; 63361</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72645; 81487</t>
+          <t>72697; 82011</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52757; 59537</t>
+          <t>52867; 59505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85681; 95209</t>
+          <t>85513; 95038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71770; 81586</t>
+          <t>71651; 81492</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63090; 71573</t>
+          <t>62469; 71549</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>144161; 156206</t>
+          <t>143537; 155631</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>148910; 161530</t>
+          <t>148237; 161824</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118789; 129365</t>
+          <t>118381; 129361</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>175930; 188829</t>
+          <t>174546; 188227</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169342; 185836</t>
+          <t>169619; 185930</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194967; 208244</t>
+          <t>195412; 209276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170209; 185398</t>
+          <t>171145; 184671</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>203223; 216575</t>
+          <t>203688; 216868</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>188421; 200705</t>
+          <t>188164; 200795</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>350571; 370262</t>
+          <t>351043; 370954</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>379092; 399347</t>
+          <t>379045; 399736</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>387463; 407026</t>
+          <t>388171; 406454</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92026; 100360</t>
+          <t>92580; 100326</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>123944; 136557</t>
+          <t>123157; 136307</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118369; 128628</t>
+          <t>118863; 128631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104668; 116851</t>
+          <t>104267; 116797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>119838; 132202</t>
+          <t>118917; 131796</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>122802; 134653</t>
+          <t>121782; 134205</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>200024; 214666</t>
+          <t>200110; 214830</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>248504; 265855</t>
+          <t>248320; 266397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>244414; 260929</t>
+          <t>244455; 260188</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>64018; 72016</t>
+          <t>64468; 71753</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44438; 51376</t>
+          <t>44534; 51417</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49922; 57391</t>
+          <t>49973; 57548</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61048; 68912</t>
+          <t>60858; 68965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61620; 69935</t>
+          <t>61200; 70069</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60766; 67163</t>
+          <t>60931; 67077</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>127184; 139653</t>
+          <t>127768; 139435</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>108701; 119884</t>
+          <t>108576; 119917</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>114211; 123272</t>
+          <t>113663; 123555</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>564286; 587975</t>
+          <t>563948; 587526</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>586162; 612749</t>
+          <t>585318; 611969</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>589905; 613995</t>
+          <t>589439; 614198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>585939; 613042</t>
+          <t>584429; 612073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>635912; 661865</t>
+          <t>635965; 661118</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>634913; 659523</t>
+          <t>632115; 658367</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1157407; 1193433</t>
+          <t>1158146; 1193323</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1229543; 1267704</t>
+          <t>1230032; 1267351</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1232980; 1267254</t>
+          <t>1233596; 1268259</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>86,67%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>87,32%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>89,28%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>85,42%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85,13%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>86,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,85; 92,04</t>
+          <t>78,32; 90,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,36; 93,99</t>
+          <t>83,43; 94,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,21; 91,26</t>
+          <t>80,09; 91,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,85; 90,35</t>
+          <t>81,15; 92,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,72; 94,44</t>
+          <t>83,24; 93,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,6; 91,22</t>
+          <t>77,33; 90,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,01; 89,96</t>
+          <t>82,21; 89,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,54; 93,08</t>
+          <t>85,2; 92,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,4; 89,82</t>
+          <t>81,4; 89,84</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>88,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>89,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>89,27%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>91,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,09; 93,32</t>
+          <t>75,09; 88,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,32; 93,79</t>
+          <t>83,55; 94,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,36; 93,27</t>
+          <t>86,34; 94,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,0; 87,88</t>
+          <t>81,98; 93,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,0; 94,31</t>
+          <t>82,83; 93,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,08; 95,02</t>
+          <t>83,75; 93,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,96; 89,59</t>
+          <t>80,99; 89,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,45; 92,78</t>
+          <t>85,56; 92,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,63; 93,05</t>
+          <t>87,04; 93,11</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91,52%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>90,03%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>90,58%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>92,21%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,09; 95,02</t>
+          <t>86,27; 95,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,38; 95,19</t>
+          <t>84,19; 94,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,49; 96,22</t>
+          <t>83,67; 94,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,09; 95,68</t>
+          <t>83,21; 95,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,08; 94,49</t>
+          <t>84,05; 94,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,82; 94,86</t>
+          <t>85,74; 96,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,46; 93,75</t>
+          <t>86,82; 93,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,98; 93,87</t>
+          <t>86,39; 93,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,24; 94,24</t>
+          <t>86,66; 94,27</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>91,04%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>86,83%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>90,61%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>88,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,95; 93,77</t>
+          <t>83,82; 91,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,3; 90,21</t>
+          <t>89,45; 95,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,4; 93,6</t>
+          <t>89,15; 95,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,69; 91,39</t>
+          <t>87,69; 94,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,68; 95,49</t>
+          <t>82,29; 90,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,24; 95,23</t>
+          <t>87,23; 93,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,15; 92,09</t>
+          <t>87,02; 92,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,49; 92,27</t>
+          <t>87,37; 92,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,35; 93,56</t>
+          <t>89,38; 93,78</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>90,4%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>93,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>88,26%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>91,26%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87,43%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>90,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,92; 96,36</t>
+          <t>81,94; 92,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,09; 91,96</t>
+          <t>84,77; 93,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,27; 94,45</t>
+          <t>85,7; 94,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,91; 91,76</t>
+          <t>88,43; 96,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,69; 93,87</t>
+          <t>83,49; 92,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,11; 93,79</t>
+          <t>86,98; 94,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,47; 92,84</t>
+          <t>86,23; 92,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>86,03; 92,29</t>
+          <t>85,64; 92,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,53; 93,16</t>
+          <t>87,59; 93,32</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89,81%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>92,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>90,13%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>88,94%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,11; 95,84</t>
+          <t>83,86; 95,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,61; 95,37</t>
+          <t>82,27; 94,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,81; 94,21</t>
+          <t>89,8; 98,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,07; 95,27</t>
+          <t>85,57; 96,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82,66; 94,64</t>
+          <t>81,2; 95,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89,84; 98,9</t>
+          <t>82,11; 94,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,76; 94,68</t>
+          <t>86,56; 94,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,86; 93,72</t>
+          <t>84,99; 93,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88,17; 95,84</t>
+          <t>88,1; 95,76</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>87,64%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>90,47%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>88,55%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>89,89%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,47; 92,17</t>
+          <t>85,52; 89,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,38; 90,31</t>
+          <t>89,09; 92,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,78; 91,47</t>
+          <t>89,27; 92,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85,37; 89,41</t>
+          <t>88,62; 92,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,12; 92,64</t>
+          <t>86,46; 90,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,06; 92,76</t>
+          <t>88,0; 91,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,6; 90,27</t>
+          <t>87,51; 90,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,41; 91,1</t>
+          <t>88,39; 91,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,31; 91,82</t>
+          <t>89,19; 91,75</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>108</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83040</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80133</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>86493</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>90485</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>80289</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>70978</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83040</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>80133</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86493</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83774; 95375</t>
+          <t>76402; 88013</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74965; 84531</t>
+          <t>74268; 83810</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64987; 75828</t>
+          <t>79924; 91137</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76910; 88132</t>
+          <t>84084; 95591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74525; 84071</t>
+          <t>74857; 84359</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79442; 91039</t>
+          <t>64252; 75422</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>164967; 180960</t>
+          <t>165386; 180667</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>153070; 166574</t>
+          <t>152471; 166097</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>148877; 164277</t>
+          <t>148879; 164304</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70879</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86904</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>102976</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>77447</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>83334</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>94372</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70879</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86904</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>102976</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72609; 81549</t>
+          <t>64553; 76391</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77707; 87475</t>
+          <t>80854; 91185</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88126; 98597</t>
+          <t>97344; 107013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64479; 75555</t>
+          <t>71644; 81352</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81289; 91268</t>
+          <t>77248; 87479</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>97057; 107126</t>
+          <t>88536; 98576</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>140349; 155315</t>
+          <t>140410; 155342</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>162401; 176315</t>
+          <t>162601; 176379</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>189262; 203285</t>
+          <t>190154; 203418</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90904</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77846</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67900</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>60034</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>78040</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>57022</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90904</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>77846</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67900</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55408; 63361</t>
+          <t>85690; 94667</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72697; 82011</t>
+          <t>72611; 81715</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52867; 59505</t>
+          <t>63110; 71494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85513; 95038</t>
+          <t>55483; 63404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71651; 81492</t>
+          <t>72417; 81528</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62469; 71549</t>
+          <t>53021; 59573</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>143537; 155631</t>
+          <t>144132; 156033</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>148237; 161824</t>
+          <t>148944; 161548</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118381; 129361</t>
+          <t>118956; 129399</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>259</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>308</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178337</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210963</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>195605</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>182742</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>178955</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>202594</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>178337</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>210963</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>195605</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>174546; 188227</t>
+          <t>169381; 184014</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169619; 185930</t>
+          <t>203162; 217026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>195412; 209276</t>
+          <t>187976; 200725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171145; 184671</t>
+          <t>176017; 188685</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>203688; 216868</t>
+          <t>169608; 186033</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>188164; 200795</t>
+          <t>195032; 208972</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>351043; 370954</t>
+          <t>350505; 371012</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>379045; 399736</t>
+          <t>378492; 398870</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>388171; 406454</t>
+          <t>388282; 407425</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>187</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>187</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>111290</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126914</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>129347</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>97014</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>130826</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>124292</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>111290</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>126914</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>129347</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92580; 100326</t>
+          <t>104302; 117313</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>123157; 136307</t>
+          <t>119031; 131968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118863; 128631</t>
+          <t>122633; 134759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104267; 116797</t>
+          <t>92071; 100427</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>118917; 131796</t>
+          <t>123760; 136717</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>121782; 134205</t>
+          <t>118464; 128885</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>200110; 214830</t>
+          <t>199536; 214806</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>248320; 266397</t>
+          <t>247189; 265564</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>244455; 260188</t>
+          <t>244633; 260614</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>66491</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64988</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>68921</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>48589</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>54332</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>65513</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>66491</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>64988</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>64468; 71753</t>
+          <t>60707; 68991</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>44534; 51417</t>
+          <t>60908; 69934</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49973; 57548</t>
+          <t>60907; 67083</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60858; 68965</t>
+          <t>64066; 72044</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61200; 70069</t>
+          <t>43778; 51231</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60931; 67077</t>
+          <t>50156; 57586</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>127768; 139435</t>
+          <t>127469; 139561</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>108576; 119917</t>
+          <t>108739; 119835</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>113663; 123555</t>
+          <t>113566; 123445</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>858</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>864</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>906</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>599964</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>649253</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>647307</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>576643</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>600034</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>603589</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>599964</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>649253</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>647307</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>563948; 587526</t>
+          <t>585450; 613220</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>585318; 611969</t>
+          <t>635726; 661605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>589439; 614198</t>
+          <t>633571; 658392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>584429; 612073</t>
+          <t>564884; 588439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>635965; 661118</t>
+          <t>585861; 612655</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>632115; 658367</t>
+          <t>590930; 616131</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1158146; 1193323</t>
+          <t>1156951; 1194105</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1230032; 1267351</t>
+          <t>1229668; 1267434</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1233596; 1268259</t>
+          <t>1231871; 1267250</t>
         </is>
       </c>
     </row>
